--- a/output/pdf_financials_xlsx/XX.xlsx
+++ b/output/pdf_financials_xlsx/XX.xlsx
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.207655</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.506212</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>2.330884</v>
@@ -2004,10 +2004,10 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.207655</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.506212</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>2.330884</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.3322</v>
+        <v>0.124545</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.556157</v>
+        <v>0.049945</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.124905</v>
@@ -5937,22 +5937,22 @@
         <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.591959</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.498036</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.560524</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.519442</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.665902</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.699823</v>
       </c>
     </row>
     <row r="125">
@@ -5980,22 +5980,22 @@
         <v>0</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.591959</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.498036</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.560524</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.519442</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.665902</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.699823</v>
       </c>
     </row>
     <row r="126">
@@ -22008,7 +22008,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -24530,7 +24530,11 @@
           <t>Principal lease payments (note 13)</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -27340,7 +27344,11 @@
           <t>Principal lease payments (note 15)</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -32660,7 +32668,11 @@
           <t>Principal lease payments (note 14)</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
           <t>-</t>
@@ -40332,7 +40344,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
@@ -52226,7 +52238,7 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
@@ -56500,7 +56512,7 @@
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
@@ -58062,7 +58074,7 @@
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
@@ -59570,7 +59582,7 @@
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E716" t="inlineStr">
@@ -62218,7 +62230,7 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
@@ -66582,7 +66594,7 @@
       </c>
       <c r="D809" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E809" t="inlineStr">

--- a/output/pdf_financials_xlsx/XX.xlsx
+++ b/output/pdf_financials_xlsx/XX.xlsx
@@ -1682,37 +1682,37 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.01359</v>
+        <v>0.011876</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.054371</v>
+        <v>0.009863</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.778517</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.530133</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.687777</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>5.089176</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.394317</v>
+        <v>1.142851</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.354217</v>
+        <v>1.196176</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>1.342255</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.557153</v>
+        <v>1.759395</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.645089</v>
+        <v>1.290178</v>
       </c>
     </row>
     <row r="29">
@@ -1727,37 +1727,37 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.6205889999999999</v>
+        <v>-0.6223030000000001</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.42519</v>
+        <v>0.380682</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.463559</v>
+        <v>1.242076</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.417414</v>
+        <v>0.947547</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.159392</v>
+        <v>-2.471615</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-3.805452</v>
+        <v>1.283724</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-4.255845</v>
+        <v>-3.507311</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-5.521895</v>
+        <v>-4.679936</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.261946</v>
+        <v>-1.919691</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.929893</v>
+        <v>-0.727651</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.015725</v>
+        <v>-0.370636</v>
       </c>
     </row>
     <row r="30">
@@ -1772,37 +1772,37 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-11.20679006995068</v>
+        <v>-11.23774201750356</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>6.302435996234458</v>
+        <v>5.642710176435302</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>2.218158853361181</v>
+        <v>5.943411466388189</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>1.788669028910418</v>
+        <v>4.060352485390955</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-9.848106736117076</v>
+        <v>-7.704244465576925</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-6.826988492445942</v>
+        <v>2.303003421269451</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-138.154627147464</v>
+        <v>-113.8554725313537</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-177.9814801623588</v>
+        <v>-150.8434941890617</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-16.34215692487819</v>
+        <v>-9.617538600968972</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-7.735108739413987</v>
+        <v>-2.916462005584417</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-3.008509752994899</v>
+        <v>-1.097799129499636</v>
       </c>
     </row>
     <row r="31">
@@ -4888,37 +4888,37 @@
         <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.011876</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.009863</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.839607</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.530133</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.687777</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>1.476268</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.394317</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.354217</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.392551</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.557153</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.645089</v>
       </c>
     </row>
     <row r="101">
@@ -23298,7 +23298,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -26612,7 +26612,11 @@
           <t>Amortization on intangible assets (note 12)</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -30064,7 +30068,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -31780,7 +31784,11 @@
           <t>Amortization on intangible assets (note 11)</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>-</t>
@@ -33938,7 +33946,11 @@
           <t>Amortization on intangible assets (note 11)</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E371" t="inlineStr">
         <is>
           <t>-</t>
@@ -35808,7 +35820,11 @@
           <t>Amortization on intangible assets (note 9)</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E396" t="inlineStr">
         <is>
           <t>-</t>
@@ -37448,7 +37464,11 @@
           <t>Depreciation on property, plant &amp; equipment $</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E418" t="inlineStr">
         <is>
           <t>-</t>
@@ -37518,7 +37538,11 @@
           <t>Amortization on intangible assets $</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -39924,7 +39948,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
@@ -44446,7 +44470,11 @@
           <t>Amortization on intangible assets - -</t>
         </is>
       </c>
-      <c r="D513" t="inlineStr"/>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E513" t="inlineStr">
         <is>
           <t>-</t>
@@ -46310,7 +46338,11 @@
           <t>Amortization on intangible assets - - 557,153</t>
         </is>
       </c>
-      <c r="D538" t="inlineStr"/>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E538" t="inlineStr">
         <is>
           <t>-</t>
@@ -48308,7 +48340,11 @@
           <t>Amortization on intangible assets (note 12)</t>
         </is>
       </c>
-      <c r="D565" t="inlineStr"/>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E565" t="inlineStr">
         <is>
           <t>-</t>
@@ -51774,7 +51810,11 @@
           <t>Amortization on intangible assets 392,551</t>
         </is>
       </c>
-      <c r="D612" t="inlineStr"/>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E612" t="inlineStr">
         <is>
           <t>-</t>
@@ -56064,7 +56104,11 @@
           <t>Amortization on intangible assets - 354,217</t>
         </is>
       </c>
-      <c r="D669" t="inlineStr"/>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E669" t="inlineStr">
         <is>
           <t>-</t>
@@ -59356,7 +59400,7 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
@@ -61848,7 +61892,11 @@
           <t>Amortization on intangible assets - 394,317</t>
         </is>
       </c>
-      <c r="D746" t="inlineStr"/>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E746" t="inlineStr">
         <is>
           <t>-</t>
@@ -64648,7 +64696,11 @@
           <t>Amortization on intangible assets (note 11)</t>
         </is>
       </c>
-      <c r="D783" t="inlineStr"/>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E783" t="inlineStr">
         <is>
           <t>-</t>
@@ -66208,7 +66260,11 @@
           <t>Amortization on intangible assets - - 3,612,908</t>
         </is>
       </c>
-      <c r="D804" t="inlineStr"/>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E804" t="inlineStr">
         <is>
           <t>-</t>
@@ -69600,7 +69656,11 @@
           <t>Amortization on intangible assets (note 12) 397,174</t>
         </is>
       </c>
-      <c r="D849" t="inlineStr"/>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E849" t="inlineStr">
         <is>
           <t>-</t>
@@ -71468,7 +71528,11 @@
           <t>Depreciation on property, plant &amp; equipment</t>
         </is>
       </c>
-      <c r="D874" t="inlineStr"/>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E874" t="inlineStr">
         <is>
           <t>-</t>
@@ -71542,7 +71606,11 @@
           <t>Amortization on intangible assets</t>
         </is>
       </c>
-      <c r="D875" t="inlineStr"/>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E875" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/XX.xlsx
+++ b/output/pdf_financials_xlsx/XX.xlsx
@@ -1303,8 +1303,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
-        <v>-0.6306890000000001</v>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D20" s="3" t="n">
         <v>0.370819</v>
@@ -1324,11 +1326,15 @@
       <c r="I20" s="3" t="n">
         <v>-2.801948</v>
       </c>
-      <c r="J20" s="3" t="n">
-        <v>-4.391903</v>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>0.03231</v>
+      <c r="J20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L20" s="3" t="n">
         <v>-2.400253</v>
@@ -1349,7 +1355,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>0.00349</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -1370,10 +1376,10 @@
         <v>0</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0</v>
+        <v>1.544975</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>3.888183</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>0</v>
@@ -5585,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.125</v>
       </c>
       <c r="G116" s="3" t="n">
         <v>0</v>
@@ -5600,7 +5606,7 @@
         <v>0</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.575</v>
       </c>
       <c r="L116" s="3" t="n">
         <v>0</v>
@@ -6139,7 +6145,7 @@
         <v>0</v>
       </c>
       <c r="J128" s="3" t="n">
-        <v>0</v>
+        <v>-0.452417</v>
       </c>
       <c r="K128" s="3" t="n">
         <v>0</v>
@@ -27712,7 +27718,11 @@
           <t>Purchase of intangible assets (note 12)</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -28810,7 +28820,11 @@
           <t>Financing fees paid</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -36868,7 +36882,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E410" t="inlineStr">
         <is>
           <t>-</t>
@@ -58880,7 +58898,11 @@
           <t>Net income from discontinued operations</t>
         </is>
       </c>
-      <c r="D706" t="inlineStr"/>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E706" t="inlineStr">
         <is>
           <t>-</t>
@@ -73970,7 +73992,11 @@
           <t>Income from discontinued operations (note 5)</t>
         </is>
       </c>
-      <c r="D906" t="inlineStr"/>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E906" t="inlineStr">
         <is>
           <t>-</t>
